--- a/app/templates/Template_Part_Livinas_Fino_Grueso.xlsx
+++ b/app/templates/Template_Part_Livinas_Fino_Grueso.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD2FDE01-C3CB-4429-A12D-AA9AC4C450B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D167AD8-75DF-450C-8E55-C99DE8E342D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1307,9 +1307,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1540,6 +1537,9 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -4198,28 +4198,28 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="159" t="s">
+      <c r="A8" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="159"/>
-      <c r="H8" s="159"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
     </row>
     <row r="9" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="160" t="s">
+      <c r="A9" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="160"/>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
+      <c r="B9" s="159"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
@@ -4267,30 +4267,30 @@
       <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="162"/>
-      <c r="C14" s="162"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="162"/>
-      <c r="F14" s="162"/>
-      <c r="G14" s="162"/>
-      <c r="H14" s="163"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="162"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="156" t="s">
+      <c r="A15" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="157"/>
-      <c r="G15" s="157"/>
-      <c r="H15" s="158"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="157"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
     </row>
@@ -4307,11 +4307,11 @@
       <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="165"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
-      <c r="F17" s="165"/>
-      <c r="G17" s="165"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="164"/>
       <c r="H17" s="45"/>
       <c r="J17" s="15"/>
     </row>
@@ -4356,14 +4356,14 @@
       <c r="J21" s="30"/>
     </row>
     <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="166" t="s">
+      <c r="A22" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="167"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="168"/>
+      <c r="B22" s="166"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="167"/>
       <c r="G22" s="76"/>
       <c r="H22" s="82"/>
       <c r="I22" s="76"/>
@@ -4519,26 +4519,26 @@
       <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="166" t="s">
+      <c r="A31" s="165" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="167"/>
-      <c r="C31" s="167"/>
-      <c r="D31" s="167"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="151"/>
+      <c r="B31" s="166"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="167"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="150"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="152" t="s">
+      <c r="A32" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="153"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="154"/>
+      <c r="B32" s="152"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="153"/>
       <c r="E32" s="7">
         <v>1</v>
       </c>
@@ -4784,11 +4784,11 @@
       <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="164"/>
-      <c r="C49" s="164"/>
-      <c r="D49" s="164"/>
-      <c r="E49" s="164"/>
-      <c r="F49" s="164"/>
+      <c r="B49" s="163"/>
+      <c r="C49" s="163"/>
+      <c r="D49" s="163"/>
+      <c r="E49" s="163"/>
+      <c r="F49" s="163"/>
       <c r="G49" s="33"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15"/>
@@ -4824,16 +4824,16 @@
     </row>
     <row r="52" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="155" t="s">
+      <c r="A53" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="155"/>
-      <c r="C53" s="155"/>
-      <c r="D53" s="155"/>
-      <c r="E53" s="155"/>
-      <c r="F53" s="155"/>
-      <c r="G53" s="155"/>
-      <c r="H53" s="155"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="154"/>
+      <c r="E53" s="154"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="154"/>
     </row>
     <row r="54" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4950,30 +4950,30 @@
       <c r="I6" s="111"/>
     </row>
     <row r="7" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="188" t="s">
+      <c r="A7" s="187" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="188"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="188"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="187"/>
     </row>
     <row r="8" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="189" t="s">
+      <c r="A8" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="189"/>
-      <c r="C8" s="189"/>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
-      <c r="G8" s="189"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="189"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="188"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="188"/>
+      <c r="G8" s="188"/>
+      <c r="H8" s="188"/>
+      <c r="I8" s="188"/>
       <c r="L8" s="102"/>
     </row>
     <row r="9" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -4988,31 +4988,31 @@
       <c r="I9" s="112"/>
     </row>
     <row r="10" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="194"/>
-      <c r="C10" s="192" t="s">
+      <c r="B10" s="193"/>
+      <c r="C10" s="191" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="193"/>
-      <c r="E10" s="191" t="s">
+      <c r="D10" s="192"/>
+      <c r="E10" s="190" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="191" t="s">
+      <c r="F10" s="190" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="192" t="s">
+      <c r="G10" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="193"/>
+      <c r="H10" s="192"/>
     </row>
     <row r="11" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="113"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="192"/>
-      <c r="D11" s="193"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="192"/>
-      <c r="H11" s="193"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="194"/>
+      <c r="F11" s="194"/>
+      <c r="G11" s="191"/>
+      <c r="H11" s="192"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -5029,30 +5029,30 @@
       <c r="I12" s="115"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="161" t="s">
+      <c r="A13" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="162"/>
-      <c r="C13" s="162"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
-      <c r="I13" s="163"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
+      <c r="F13" s="161"/>
+      <c r="G13" s="161"/>
+      <c r="H13" s="161"/>
+      <c r="I13" s="162"/>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="155" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
-      <c r="F14" s="157"/>
-      <c r="G14" s="157"/>
-      <c r="H14" s="157"/>
-      <c r="I14" s="158"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="157"/>
     </row>
     <row r="15" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="116"/>
@@ -5067,361 +5067,361 @@
     </row>
     <row r="16" spans="1:12" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="119"/>
-      <c r="D16" s="174" t="s">
+      <c r="D16" s="173" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="174"/>
-      <c r="F16" s="174"/>
-      <c r="G16" s="149"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="148"/>
       <c r="I16" s="120"/>
       <c r="L16" s="121"/>
     </row>
     <row r="17" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="127"/>
-      <c r="B18" s="173" t="s">
+      <c r="A18" s="126"/>
+      <c r="B18" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="173"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="173"/>
-      <c r="I18" s="127"/>
+      <c r="C18" s="172"/>
+      <c r="D18" s="172"/>
+      <c r="E18" s="172"/>
+      <c r="F18" s="172"/>
+      <c r="G18" s="172"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="126"/>
       <c r="K18" s="104"/>
     </row>
     <row r="19" spans="1:16" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="127"/>
+      <c r="A19" s="126"/>
       <c r="B19" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="177" t="s">
+      <c r="C19" s="176" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="178"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="177"/>
+      <c r="F19" s="178"/>
       <c r="G19" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="124">
+      <c r="H19" s="195">
         <v>215</v>
       </c>
-      <c r="I19" s="127"/>
-      <c r="J19" s="125"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="124"/>
       <c r="K19" s="105"/>
     </row>
     <row r="20" spans="1:16" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="127"/>
+      <c r="A20" s="126"/>
       <c r="B20" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="177" t="s">
+      <c r="C20" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="178"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="178"/>
       <c r="G20" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="124">
+      <c r="H20" s="195">
         <v>0.87</v>
       </c>
-      <c r="I20" s="127"/>
-      <c r="J20" s="125"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="124"/>
       <c r="K20" s="105"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="126"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="125"/>
     </row>
     <row r="21" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="127"/>
+      <c r="A21" s="126"/>
       <c r="B21" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="177" t="s">
+      <c r="C21" s="176" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="178"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="178"/>
       <c r="G21" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="H21" s="124">
+      <c r="H21" s="195">
         <f>H20/H19*100</f>
         <v>0.40465116279069763</v>
       </c>
-      <c r="I21" s="127"/>
-      <c r="J21" s="125"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="124"/>
       <c r="K21" s="105"/>
     </row>
     <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="127"/>
-      <c r="B22" s="127"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="125"/>
+      <c r="A22" s="126"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="126"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="124"/>
       <c r="K22" s="105"/>
     </row>
     <row r="23" spans="1:16" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="127"/>
-      <c r="B23" s="173" t="s">
+      <c r="A23" s="126"/>
+      <c r="B23" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="173"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="173"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="172"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
       <c r="J23" s="38"/>
     </row>
     <row r="24" spans="1:16" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="127"/>
-      <c r="B24" s="128" t="s">
+      <c r="A24" s="126"/>
+      <c r="B24" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="180" t="s">
+      <c r="C24" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="180"/>
-      <c r="E24" s="130" t="s">
+      <c r="D24" s="179"/>
+      <c r="E24" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="129" t="s">
+      <c r="F24" s="128" t="s">
         <v>66</v>
       </c>
-      <c r="G24" s="129" t="s">
+      <c r="G24" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
       <c r="J24" s="38"/>
     </row>
     <row r="25" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="127"/>
+      <c r="A25" s="126"/>
       <c r="B25" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="131">
+      <c r="C25" s="130">
         <v>2</v>
       </c>
-      <c r="D25" s="131" t="s">
+      <c r="D25" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="132" t="s">
+      <c r="E25" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="133"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
       <c r="J25" s="38"/>
     </row>
     <row r="26" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="127"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="131">
+      <c r="C26" s="130">
         <v>1</v>
       </c>
-      <c r="D26" s="135">
+      <c r="D26" s="134">
         <v>1.5</v>
       </c>
-      <c r="E26" s="132" t="s">
+      <c r="E26" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="133"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="127"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="126"/>
+      <c r="I26" s="126"/>
       <c r="J26" s="38"/>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="127"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="135">
+      <c r="C27" s="134">
         <v>0.5</v>
       </c>
-      <c r="D27" s="135">
+      <c r="D27" s="134">
         <v>0.75</v>
       </c>
-      <c r="E27" s="132" t="s">
+      <c r="E27" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="133"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
       <c r="J27" s="38"/>
     </row>
     <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="127"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="181">
+      <c r="C28" s="180">
         <v>0.375</v>
       </c>
-      <c r="D28" s="182"/>
-      <c r="E28" s="132" t="s">
+      <c r="D28" s="181"/>
+      <c r="E28" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="133"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="126"/>
       <c r="J28" s="38"/>
     </row>
     <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="127"/>
+      <c r="A29" s="126"/>
       <c r="B29" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="183" t="s">
+      <c r="C29" s="182" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="184"/>
-      <c r="E29" s="132" t="s">
+      <c r="D29" s="183"/>
+      <c r="E29" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
       <c r="J29" s="38"/>
     </row>
     <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="127"/>
+      <c r="A30" s="126"/>
       <c r="B30" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="182" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="136" t="s">
+      <c r="D30" s="183"/>
+      <c r="E30" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="185"/>
-      <c r="G30" s="186"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="137"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="126"/>
+      <c r="I30" s="126"/>
+      <c r="J30" s="136"/>
     </row>
     <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="127"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="138"/>
+      <c r="A31" s="126"/>
+      <c r="B31" s="126"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="126"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="137"/>
     </row>
     <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="127"/>
-      <c r="B32" s="127"/>
-      <c r="C32" s="187" t="s">
+      <c r="A32" s="126"/>
+      <c r="B32" s="126"/>
+      <c r="C32" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="187"/>
-      <c r="E32" s="187"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
+      <c r="D32" s="186"/>
+      <c r="E32" s="186"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="126"/>
+      <c r="I32" s="126"/>
     </row>
     <row r="33" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="127"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="169" t="s">
+      <c r="A33" s="126"/>
+      <c r="B33" s="126"/>
+      <c r="C33" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="170"/>
-      <c r="E33" s="171" t="s">
+      <c r="D33" s="169"/>
+      <c r="E33" s="170" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
+      <c r="H33" s="126"/>
+      <c r="I33" s="126"/>
     </row>
     <row r="34" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="139" t="s">
+      <c r="A34" s="126"/>
+      <c r="B34" s="126"/>
+      <c r="C34" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="139" t="s">
+      <c r="D34" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="172"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
+      <c r="E34" s="171"/>
+      <c r="H34" s="126"/>
+      <c r="I34" s="126"/>
     </row>
     <row r="35" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="127"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="140" t="s">
+      <c r="A35" s="126"/>
+      <c r="B35" s="126"/>
+      <c r="C35" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="140">
+      <c r="D35" s="139">
         <v>4.75</v>
       </c>
-      <c r="E35" s="140">
+      <c r="E35" s="139">
         <v>200</v>
       </c>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
+      <c r="H35" s="126"/>
+      <c r="I35" s="126"/>
     </row>
     <row r="36" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="127"/>
-      <c r="B36" s="127"/>
-      <c r="C36" s="140" t="s">
+      <c r="A36" s="126"/>
+      <c r="B36" s="126"/>
+      <c r="C36" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="140">
+      <c r="D36" s="139">
         <v>9.5</v>
       </c>
-      <c r="E36" s="140">
+      <c r="E36" s="139">
         <v>1500</v>
       </c>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="126"/>
     </row>
     <row r="37" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="127"/>
-      <c r="B37" s="127"/>
-      <c r="C37" s="140" t="s">
+      <c r="A37" s="126"/>
+      <c r="B37" s="126"/>
+      <c r="C37" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="140" t="s">
+      <c r="D37" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="140">
+      <c r="E37" s="139">
         <v>3000</v>
       </c>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
+      <c r="H37" s="126"/>
+      <c r="I37" s="126"/>
     </row>
     <row r="38" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="127"/>
-      <c r="B38" s="127"/>
-      <c r="C38" s="140" t="s">
+      <c r="A38" s="126"/>
+      <c r="B38" s="126"/>
+      <c r="C38" s="139" t="s">
         <v>50</v>
       </c>
       <c r="D38" s="122" t="s">
@@ -5430,13 +5430,13 @@
       <c r="E38" s="122">
         <v>5000</v>
       </c>
-      <c r="H38" s="127"/>
-      <c r="I38" s="127"/>
+      <c r="H38" s="126"/>
+      <c r="I38" s="126"/>
     </row>
     <row r="39" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="127"/>
-      <c r="B39" s="127"/>
-      <c r="C39" s="140" t="s">
+      <c r="A39" s="126"/>
+      <c r="B39" s="126"/>
+      <c r="C39" s="139" t="s">
         <v>51</v>
       </c>
       <c r="D39" s="122" t="s">
@@ -5445,52 +5445,52 @@
       <c r="E39" s="122">
         <v>10000</v>
       </c>
-      <c r="H39" s="127"/>
-      <c r="I39" s="127"/>
+      <c r="H39" s="126"/>
+      <c r="I39" s="126"/>
     </row>
     <row r="40" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="127"/>
-      <c r="B40" s="127"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
+      <c r="A40" s="126"/>
+      <c r="B40" s="126"/>
+      <c r="C40" s="126"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="126"/>
+      <c r="G40" s="126"/>
+      <c r="H40" s="126"/>
+      <c r="I40" s="126"/>
     </row>
     <row r="41" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="126"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="143"/>
-      <c r="I41" s="138"/>
+      <c r="B41" s="125"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="137"/>
     </row>
     <row r="42" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="144"/>
-      <c r="B42" s="144"/>
+      <c r="A42" s="143"/>
+      <c r="B42" s="143"/>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
-      <c r="H42" s="145"/>
+      <c r="H42" s="144"/>
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="176"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
-      <c r="G43" s="176"/>
-      <c r="H43" s="146"/>
+      <c r="C43" s="175"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="175"/>
+      <c r="F43" s="175"/>
+      <c r="G43" s="175"/>
+      <c r="H43" s="145"/>
       <c r="I43" s="38"/>
     </row>
     <row r="44" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="146"/>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
       <c r="E44" s="38"/>
@@ -5500,10 +5500,10 @@
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="148" t="s">
+      <c r="A45" s="147" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="147"/>
+      <c r="B45" s="146"/>
       <c r="C45" s="38"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -5514,17 +5514,17 @@
     </row>
     <row r="46" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="175" t="s">
+      <c r="A47" s="174" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="175"/>
-      <c r="C47" s="175"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="175"/>
-      <c r="F47" s="175"/>
-      <c r="G47" s="175"/>
-      <c r="H47" s="175"/>
-      <c r="I47" s="175"/>
+      <c r="B47" s="174"/>
+      <c r="C47" s="174"/>
+      <c r="D47" s="174"/>
+      <c r="E47" s="174"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="174"/>
+      <c r="H47" s="174"/>
+      <c r="I47" s="174"/>
     </row>
     <row r="48" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5584,10 +5584,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="190"/>
+      <c r="B2" s="189"/>
       <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
